--- a/app/backends/sveltekit/template/ExpenseReport.xlsx
+++ b/app/backends/sveltekit/template/ExpenseReport.xlsx
@@ -1,23 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28925"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{386E1547-6D12-4E99-A96A-3AC9DD798293}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8659F5F2-D48F-429D-AFA2-21230E706242}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5916" yWindow="3540" windowWidth="20304" windowHeight="12696" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="27288" windowHeight="17544" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Expense Express" sheetId="1" r:id="rId1"/>
-    <sheet name="Expense Report" sheetId="2" r:id="rId2"/>
+    <sheet name="Expense Report" sheetId="2" r:id="rId1"/>
   </sheets>
   <calcPr calcId="171027"/>
-  <fileRecoveryPr repairLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="10">
   <si>
     <t>IDS</t>
   </si>
@@ -44,16 +42,20 @@
   </si>
   <si>
     <t>SPENT</t>
+  </si>
+  <si>
+    <t>OVERSPENT</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
+  <numFmts count="2">
+    <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="164" formatCode="_([$NGN]\ * #,##0.00_);_([$NGN]\ * \(#,##0.00\);_([$NGN]\ * &quot;-&quot;??_);_(@_)"/>
   </numFmts>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -62,6 +64,22 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
@@ -77,7 +95,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -85,20 +103,245 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="2" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="44" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="18">
+    <dxf>
+      <font>
+        <b/>
+      </font>
+      <numFmt numFmtId="34" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+      <numFmt numFmtId="34" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+      <numFmt numFmtId="30" formatCode="@"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="0"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="0"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="0"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="34" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="0"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="30" formatCode="@"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="0"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="30" formatCode="@"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="0"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="0"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="0"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="0"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="0"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -112,29 +355,30 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table1" displayName="Table1" ref="A1:F1" headerRowCount="0">
-  <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="IDS"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="DATE"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="EXPENSE"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="DESCRIPTIONS"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="AMOUNT"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="BALANCE"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="summary" displayName="summary" ref="A1:E2" headerRowCount="0" headerRowDxfId="12" dataDxfId="10" totalsRowDxfId="11">
+  <tableColumns count="5">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="ID" dataDxfId="14"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="EXPENSES" dataDxfId="2"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="AMOUNT" dataDxfId="1"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0100-000004000000}" name="SPENT" dataDxfId="0"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0100-000005000000}" name="BALANCE" dataDxfId="13"/>
   </tableColumns>
-  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+  <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="Table2" displayName="Table2" ref="A1:E1" headerRowCount="0">
-  <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="ID"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="EXPENSES"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="AMOUNT"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0100-000004000000}" name="SPENT"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0100-000005000000}" name="BALANCE"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{FC06EC1B-22B8-4CCF-A575-7665E8D5DE52}" name="express" displayName="express" ref="A7:G8" headerRowCount="0" headerRowDxfId="17" dataDxfId="15" totalsRowDxfId="16">
+  <tableColumns count="7">
+    <tableColumn id="1" xr3:uid="{A2BAF173-0C08-4516-AD1C-C6A5C4FF9302}" name="IDS" dataDxfId="9"/>
+    <tableColumn id="2" xr3:uid="{9E7A1990-B5E2-4298-A9E5-A1E86E6D2F72}" name="DATE" dataDxfId="8"/>
+    <tableColumn id="3" xr3:uid="{420360E1-F134-4680-A2DE-C1D6693BD9B6}" name="EXPENSE" dataDxfId="7"/>
+    <tableColumn id="4" xr3:uid="{655F826C-1EBA-459C-8652-3E7A16E1350D}" name="DESCRIPTIONS" dataDxfId="6"/>
+    <tableColumn id="5" xr3:uid="{4A28B5F6-4DAD-4362-8BE8-5BC03F996FA5}" name="AMOUNT" dataDxfId="5"/>
+    <tableColumn id="6" xr3:uid="{4A8036CD-EC70-47F7-AFF1-7FE5342A43B8}" name="BALANCE" dataDxfId="4"/>
+    <tableColumn id="7" xr3:uid="{7752C837-4F9F-4254-98A6-16BCF0675936}" name="Column1" dataDxfId="3"/>
   </tableColumns>
-  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+  <tableStyleInfo name="TableStyleDark5" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
@@ -454,78 +698,79 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F1"/>
-  <sheetFormatPr defaultRowHeight="14.4" customHeight="1" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="10.33203125" style="1" customWidth="1"/>
-    <col min="2" max="2" width="29.77734375" style="2" customWidth="1"/>
-    <col min="3" max="3" width="33.88671875" customWidth="1"/>
-    <col min="4" max="4" width="18.21875" customWidth="1"/>
-    <col min="5" max="5" width="24.5546875" style="3" customWidth="1"/>
-    <col min="6" max="6" width="19.77734375" style="3" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:6" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <tableParts count="1">
-    <tablePart r:id="rId1"/>
-  </tableParts>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:E1"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr defaultRowHeight="14.4" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="24.21875" customWidth="1"/>
     <col min="3" max="3" width="21.109375" customWidth="1"/>
-    <col min="4" max="4" width="21.109375" style="3" customWidth="1"/>
-    <col min="5" max="5" width="24" style="3" customWidth="1"/>
+    <col min="4" max="4" width="21.109375" style="1" customWidth="1"/>
+    <col min="5" max="5" width="24" style="1" customWidth="1"/>
+    <col min="6" max="6" width="17.88671875" customWidth="1"/>
+    <col min="7" max="7" width="14.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
+    <row r="1" spans="1:7" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="5" t="s">
         <v>5</v>
       </c>
+    </row>
+    <row r="2" spans="1:7" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="6"/>
+      <c r="B2" s="12"/>
+      <c r="C2" s="14"/>
+      <c r="D2" s="14"/>
+      <c r="E2" s="7"/>
+    </row>
+    <row r="7" spans="1:7" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B7" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="C7" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="D7" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="E7" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G7" s="8" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="2"/>
+      <c r="B8" s="8"/>
+      <c r="C8" s="9"/>
+      <c r="D8" s="9"/>
+      <c r="E8" s="10"/>
+      <c r="F8" s="3"/>
+      <c r="G8" s="8"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <tableParts count="1">
+  <tableParts count="2">
     <tablePart r:id="rId1"/>
+    <tablePart r:id="rId2"/>
   </tableParts>
 </worksheet>
 </file>
--- a/app/backends/sveltekit/template/ExpenseReport.xlsx
+++ b/app/backends/sveltekit/template/ExpenseReport.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28925"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8659F5F2-D48F-429D-AFA2-21230E706242}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B86A0AA-0D8B-4145-B77E-8F70761BB07E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="27288" windowHeight="17544" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="7560" yWindow="7668" windowWidth="17220" windowHeight="9660" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Expense Report" sheetId="2" r:id="rId1"/>
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="12">
   <si>
     <t>IDS</t>
   </si>
@@ -45,6 +45,12 @@
   </si>
   <si>
     <t>OVERSPENT</t>
+  </si>
+  <si>
+    <t>RECEIPT_DATE</t>
+  </si>
+  <si>
+    <t>BANK NAME</t>
   </si>
 </sst>
 </file>
@@ -122,7 +128,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -131,27 +137,274 @@
     <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="44" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="44" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="18">
-    <dxf>
-      <font>
-        <b/>
+  <dxfs count="24">
+    <dxf>
+      <font>
+        <b/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="0"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="30" formatCode="@"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="0"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="30" formatCode="@"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="0"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="0"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="0"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="0"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="0"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="0"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="0"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
       </font>
       <numFmt numFmtId="34" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
     </dxf>
     <dxf>
       <font>
         <b/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="0"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="30" formatCode="@"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="0"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="30" formatCode="@"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="0"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="0"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="0"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="0"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="0"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
       </font>
       <numFmt numFmtId="34" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
     </dxf>
@@ -159,186 +412,32 @@
       <font>
         <b/>
       </font>
+      <numFmt numFmtId="34" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
       <numFmt numFmtId="30" formatCode="@"/>
     </dxf>
     <dxf>
       <font>
         <b/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="0"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="0"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="0"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="34" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="0"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="30" formatCode="@"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="0"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="30" formatCode="@"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="0"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="0"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="0"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="0"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="0"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
       </font>
     </dxf>
   </dxfs>
@@ -355,28 +454,30 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="summary" displayName="summary" ref="A1:E2" headerRowCount="0" headerRowDxfId="12" dataDxfId="10" totalsRowDxfId="11">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="summary" displayName="summary" ref="A1:E2" headerRowCount="0" headerRowDxfId="23" dataDxfId="22" totalsRowDxfId="21">
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="ID" dataDxfId="14"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="EXPENSES" dataDxfId="2"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="AMOUNT" dataDxfId="1"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0100-000004000000}" name="SPENT" dataDxfId="0"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0100-000005000000}" name="BALANCE" dataDxfId="13"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="ID" dataDxfId="20"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="EXPENSES" dataDxfId="19"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="AMOUNT" dataDxfId="18"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0100-000004000000}" name="SPENT" dataDxfId="17"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0100-000005000000}" name="BALANCE" dataDxfId="16"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{FC06EC1B-22B8-4CCF-A575-7665E8D5DE52}" name="express" displayName="express" ref="A7:G8" headerRowCount="0" headerRowDxfId="17" dataDxfId="15" totalsRowDxfId="16">
-  <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{A2BAF173-0C08-4516-AD1C-C6A5C4FF9302}" name="IDS" dataDxfId="9"/>
-    <tableColumn id="2" xr3:uid="{9E7A1990-B5E2-4298-A9E5-A1E86E6D2F72}" name="DATE" dataDxfId="8"/>
-    <tableColumn id="3" xr3:uid="{420360E1-F134-4680-A2DE-C1D6693BD9B6}" name="EXPENSE" dataDxfId="7"/>
-    <tableColumn id="4" xr3:uid="{655F826C-1EBA-459C-8652-3E7A16E1350D}" name="DESCRIPTIONS" dataDxfId="6"/>
-    <tableColumn id="5" xr3:uid="{4A28B5F6-4DAD-4362-8BE8-5BC03F996FA5}" name="AMOUNT" dataDxfId="5"/>
-    <tableColumn id="6" xr3:uid="{4A8036CD-EC70-47F7-AFF1-7FE5342A43B8}" name="BALANCE" dataDxfId="4"/>
-    <tableColumn id="7" xr3:uid="{7752C837-4F9F-4254-98A6-16BCF0675936}" name="Column1" dataDxfId="3"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{FC06EC1B-22B8-4CCF-A575-7665E8D5DE52}" name="express" displayName="express" ref="A7:I8" headerRowCount="0" headerRowDxfId="15" dataDxfId="14" totalsRowDxfId="13">
+  <tableColumns count="9">
+    <tableColumn id="1" xr3:uid="{A2BAF173-0C08-4516-AD1C-C6A5C4FF9302}" name="IDS" dataDxfId="12"/>
+    <tableColumn id="2" xr3:uid="{9E7A1990-B5E2-4298-A9E5-A1E86E6D2F72}" name="DATE" dataDxfId="11"/>
+    <tableColumn id="3" xr3:uid="{420360E1-F134-4680-A2DE-C1D6693BD9B6}" name="EXPENSE" dataDxfId="10"/>
+    <tableColumn id="4" xr3:uid="{655F826C-1EBA-459C-8652-3E7A16E1350D}" name="DESCRIPTIONS" dataDxfId="9"/>
+    <tableColumn id="5" xr3:uid="{4A28B5F6-4DAD-4362-8BE8-5BC03F996FA5}" name="AMOUNT" dataDxfId="8"/>
+    <tableColumn id="6" xr3:uid="{4A8036CD-EC70-47F7-AFF1-7FE5342A43B8}" name="BALANCE" dataDxfId="7"/>
+    <tableColumn id="7" xr3:uid="{7752C837-4F9F-4254-98A6-16BCF0675936}" name="Column1" dataDxfId="2"/>
+    <tableColumn id="8" xr3:uid="{0B3F8F16-1F87-4BF7-BFBF-B27063C748AA}" name="Column2" headerRowDxfId="6" dataDxfId="1" totalsRowDxfId="5"/>
+    <tableColumn id="9" xr3:uid="{81CFF06D-4A0D-4F57-B598-ECCDA614685B}" name="Column3" headerRowDxfId="4" dataDxfId="0" totalsRowDxfId="3"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleDark5" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -699,7 +800,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:I8"/>
   <sheetFormatPr defaultRowHeight="14.4" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="24.21875" customWidth="1"/>
@@ -708,9 +809,11 @@
     <col min="5" max="5" width="24" style="1" customWidth="1"/>
     <col min="6" max="6" width="17.88671875" customWidth="1"/>
     <col min="7" max="7" width="14.6640625" customWidth="1"/>
+    <col min="8" max="8" width="20.109375" style="15" customWidth="1"/>
+    <col min="9" max="9" width="17.44140625" style="15" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="4" t="s">
         <v>6</v>
       </c>
@@ -727,14 +830,14 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="6"/>
       <c r="B2" s="12"/>
       <c r="C2" s="14"/>
       <c r="D2" s="14"/>
       <c r="E2" s="7"/>
     </row>
-    <row r="7" spans="1:7" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
         <v>0</v>
       </c>
@@ -756,8 +859,14 @@
       <c r="G7" s="8" t="s">
         <v>9</v>
       </c>
+      <c r="H7" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="I7" s="9" t="s">
+        <v>11</v>
+      </c>
     </row>
-    <row r="8" spans="1:7" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="2"/>
       <c r="B8" s="8"/>
       <c r="C8" s="9"/>
@@ -765,6 +874,8 @@
       <c r="E8" s="10"/>
       <c r="F8" s="3"/>
       <c r="G8" s="8"/>
+      <c r="H8" s="9"/>
+      <c r="I8" s="9"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
